--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify CSRF token validation on POST form submissions</t>
+          <t>CSRF Security Token Validation on POST Actions</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify CSRF token validation on POST form submissions' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'CSRF Security Token Validation on POST Actions' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify live slouch counter increments when slouch duration exceeds 5s</t>
+          <t>Slouch Event Counter Trigger on 5s Continuous Slouch</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify live slouch counter increments when slouch duration exceeds 5s' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Slouch Event Counter Trigger on 5s Continuous Slouch' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify dashboard chart image export to PNG button</t>
+          <t>Chart Vector Image PNG Export Trigger Button</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify dashboard chart image export to PNG button' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Chart Vector Image PNG Export Trigger Button' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify mark all notifications as read button updates UI badge</t>
+          <t>Mark All Notifications as Read Action Button</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify mark all notifications as read button updates UI badge' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Mark All Notifications as Read Action Button' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify report preview modal displays accurate multi-page preview</t>
+          <t>Multi-Page Report Preview Dialog Modal Render</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify report preview modal displays accurate multi-page preview' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Multi-Page Report Preview Dialog Modal Render' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify phone number field enforces international E.164 format (+1234567890)</t>
+          <t>E.164 International Phone Format Validation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify phone number field enforces international E.164 format (+1234567890)' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'E.164 International Phone Format Validation' failed visual tolerance check</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify font size scaling dynamically across desktop, tablet, and mobile breakpoints</t>
+          <t>Fluid Typography Clamp Font Size Scaling</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AssertionError: Expected element for 'Verify font size scaling dynamically across desktop, tablet, and mobile breakpoints' failed visual tolerance check</t>
+          <t>AssertionError: Expected element for 'Fluid Typography Clamp Font Size Scaling' failed visual tolerance check</t>
         </is>
       </c>
     </row>
